--- a/uploads/EOLT - Kaizen Suggestion(1-181).xlsx
+++ b/uploads/EOLT - Kaizen Suggestion(1-181).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
